--- a/data/ayesicena-matrix.xlsx
+++ b/data/ayesicena-matrix.xlsx
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P154"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="18" min="1" max="1"/>
@@ -11911,31 +11911,1558 @@
         <v/>
       </c>
     </row>
-    <row r="152"/>
+    <row r="152">
+      <c r="A152" s="27" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="27" t="inlineStr">
+        <is>
+          <t>Torta Tres Leches, Whisky</t>
+        </is>
+      </c>
+      <c r="C152" s="27" t="inlineStr">
+        <is>
+          <t>Tres leches</t>
+        </is>
+      </c>
+      <c r="D152" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E152" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F152" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: whisky in the three-milk soak and a burnt-sugar top. Assembles a day ahead and cuts to any headcount.</t>
+        </is>
+      </c>
+      <c r="G152" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H152" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I152" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J152" s="27" t="inlineStr">
+        <is>
+          <t>Leche evaporada, leche condensada, crema, whisky</t>
+        </is>
+      </c>
+      <c r="K152" s="27" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="L152" s="28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M152" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="N152" s="30">
+        <f>IFERROR(L152/M152,"")</f>
+        <v/>
+      </c>
+      <c r="O152" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P152" s="31">
+        <f>IF(N152="","",IF(N152&gt;0.32,"Reprice or resource",IF(N152&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
     <row r="153">
-      <c r="B153" s="22" t="inlineStr">
-        <is>
-          <t>Portfolio average</t>
-        </is>
-      </c>
-      <c r="L153" s="13">
-        <f>AVERAGE(L2:L151)</f>
-        <v/>
-      </c>
-      <c r="M153" s="13">
-        <f>AVERAGE(M2:M151)</f>
-        <v/>
-      </c>
-      <c r="N153" s="14">
-        <f>AVERAGE(N2:N151)</f>
+      <c r="A153" s="27" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="27" t="inlineStr">
+        <is>
+          <t>Lucuma Victoria Sponge</t>
+        </is>
+      </c>
+      <c r="C153" s="27" t="inlineStr">
+        <is>
+          <t>Victoria sponge</t>
+        </is>
+      </c>
+      <c r="D153" s="27" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E153" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F153" s="27" t="inlineStr">
+        <is>
+          <t>The English tea cake with lucuma curd and cream in the middle instead of raspberry jam.</t>
+        </is>
+      </c>
+      <c r="G153" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H153" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I153" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J153" s="27" t="inlineStr">
+        <is>
+          <t>Harina, mantequilla, huevo, lucuma</t>
+        </is>
+      </c>
+      <c r="K153" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L153" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M153" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="N153" s="30">
+        <f>IFERROR(L153/M153,"")</f>
+        <v/>
+      </c>
+      <c r="O153" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P153" s="31">
+        <f>IF(N153="","",IF(N153&gt;0.32,"Reprice or resource",IF(N153&lt;0.2,"Check cost is realistic","OK")))</f>
         <v/>
       </c>
     </row>
     <row r="154">
-      <c r="B154" s="15" t="inlineStr">
-        <is>
-          <t>Costs are unverified estimates - replace after a market run.</t>
-        </is>
+      <c r="A154" s="27" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="27" t="inlineStr">
+        <is>
+          <t>Cacao Celebration Cake</t>
+        </is>
+      </c>
+      <c r="C154" s="27" t="inlineStr">
+        <is>
+          <t>Chocolate celebration cake</t>
+        </is>
+      </c>
+      <c r="D154" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E154" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F154" s="27" t="inlineStr">
+        <is>
+          <t>Four layers of Peruvian 70% cacao sponge with chancaca buttercream. The birthday and wedding product.</t>
+        </is>
+      </c>
+      <c r="G154" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H154" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I154" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J154" s="27" t="inlineStr">
+        <is>
+          <t>Cacao, harina, mantequilla, chancaca</t>
+        </is>
+      </c>
+      <c r="K154" s="27" t="inlineStr">
+        <is>
+          <t>Cacao distributor; Makro</t>
+        </is>
+      </c>
+      <c r="L154" s="28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M154" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="N154" s="30">
+        <f>IFERROR(L154/M154,"")</f>
+        <v/>
+      </c>
+      <c r="O154" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P154" s="31">
+        <f>IF(N154="","",IF(N154&gt;0.32,"Reprice or resource",IF(N154&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="27" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="27" t="inlineStr">
+        <is>
+          <t>Carrot &amp; Kiwicha Cake</t>
+        </is>
+      </c>
+      <c r="C155" s="27" t="inlineStr">
+        <is>
+          <t>Carrot cake</t>
+        </is>
+      </c>
+      <c r="D155" s="27" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E155" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F155" s="27" t="inlineStr">
+        <is>
+          <t>Kiwicha in the batter for texture, queso fresco frosting in place of the usual cream cheese.</t>
+        </is>
+      </c>
+      <c r="G155" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H155" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I155" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J155" s="27" t="inlineStr">
+        <is>
+          <t>Zanahoria, kiwicha, queso fresco, canela</t>
+        </is>
+      </c>
+      <c r="K155" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L155" s="28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M155" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="N155" s="30">
+        <f>IFERROR(L155/M155,"")</f>
+        <v/>
+      </c>
+      <c r="O155" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P155" s="31">
+        <f>IF(N155="","",IF(N155&gt;0.32,"Reprice or resource",IF(N155&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="27" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="27" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Pecan Cake</t>
+        </is>
+      </c>
+      <c r="C156" s="27" t="inlineStr">
+        <is>
+          <t>Coffee and walnut cake</t>
+        </is>
+      </c>
+      <c r="D156" s="27" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E156" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F156" s="27" t="inlineStr">
+        <is>
+          <t>Chanchamayo coffee and pecans for walnuts. The cake that sells itself at an afternoon booking.</t>
+        </is>
+      </c>
+      <c r="G156" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H156" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I156" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J156" s="27" t="inlineStr">
+        <is>
+          <t>Cafe, pecanas, harina, mantequilla</t>
+        </is>
+      </c>
+      <c r="K156" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L156" s="28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M156" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N156" s="30">
+        <f>IFERROR(L156/M156,"")</f>
+        <v/>
+      </c>
+      <c r="O156" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P156" s="31">
+        <f>IF(N156="","",IF(N156&gt;0.32,"Reprice or resource",IF(N156&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="27" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="27" t="inlineStr">
+        <is>
+          <t>Torta Helada de Aguaymanto</t>
+        </is>
+      </c>
+      <c r="C157" s="27" t="inlineStr">
+        <is>
+          <t>Torta helada</t>
+        </is>
+      </c>
+      <c r="D157" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E157" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F157" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: the Lima jelly cake rebuilt on aguaymanto with an oat sponge under it.</t>
+        </is>
+      </c>
+      <c r="G157" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H157" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I157" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J157" s="27" t="inlineStr">
+        <is>
+          <t>Aguaymanto, gelatina, crema, avena</t>
+        </is>
+      </c>
+      <c r="K157" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; Makro</t>
+        </is>
+      </c>
+      <c r="L157" s="28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M157" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="N157" s="30">
+        <f>IFERROR(L157/M157,"")</f>
+        <v/>
+      </c>
+      <c r="O157" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P157" s="31">
+        <f>IF(N157="","",IF(N157&gt;0.32,"Reprice or resource",IF(N157&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="27" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="27" t="inlineStr">
+        <is>
+          <t>Cacao &amp; Olive Oil Cake (vegan)</t>
+        </is>
+      </c>
+      <c r="C158" s="27" t="inlineStr">
+        <is>
+          <t>Olive oil chocolate cake</t>
+        </is>
+      </c>
+      <c r="D158" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E158" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F158" s="27" t="inlineStr">
+        <is>
+          <t>No dairy, no egg, no compromise: olive oil, cacao and chicha morada make a darker cake than butter does.</t>
+        </is>
+      </c>
+      <c r="G158" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H158" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I158" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J158" s="27" t="inlineStr">
+        <is>
+          <t>Cacao, aceite de oliva, harina, maiz morado</t>
+        </is>
+      </c>
+      <c r="K158" s="27" t="inlineStr">
+        <is>
+          <t>Cacao distributor; Makro</t>
+        </is>
+      </c>
+      <c r="L158" s="28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M158" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="N158" s="30">
+        <f>IFERROR(L158/M158,"")</f>
+        <v/>
+      </c>
+      <c r="O158" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P158" s="31">
+        <f>IF(N158="","",IF(N158&gt;0.32,"Reprice or resource",IF(N158&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="27" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="27" t="inlineStr">
+        <is>
+          <t>Quinoa &amp; Almond Torte</t>
+        </is>
+      </c>
+      <c r="C159" s="27" t="inlineStr">
+        <is>
+          <t>Almond torte</t>
+        </is>
+      </c>
+      <c r="D159" s="27" t="inlineStr">
+        <is>
+          <t>Basque</t>
+        </is>
+      </c>
+      <c r="E159" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F159" s="27" t="inlineStr">
+        <is>
+          <t>Quinoa flour and ground almond, no wheat at all. The coeliac answer that is not an apology.</t>
+        </is>
+      </c>
+      <c r="G159" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H159" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I159" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J159" s="27" t="inlineStr">
+        <is>
+          <t>Quinua, almendra, huevo, azucar</t>
+        </is>
+      </c>
+      <c r="K159" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L159" s="28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M159" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="N159" s="30">
+        <f>IFERROR(L159/M159,"")</f>
+        <v/>
+      </c>
+      <c r="O159" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P159" s="31">
+        <f>IF(N159="","",IF(N159&gt;0.32,"Reprice or resource",IF(N159&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="27" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="27" t="inlineStr">
+        <is>
+          <t>Chirimoya Pavlova</t>
+        </is>
+      </c>
+      <c r="C160" s="27" t="inlineStr">
+        <is>
+          <t>Pavlova</t>
+        </is>
+      </c>
+      <c r="D160" s="27" t="inlineStr">
+        <is>
+          <t>Nordic</t>
+        </is>
+      </c>
+      <c r="E160" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F160" s="27" t="inlineStr">
+        <is>
+          <t>Meringue, cream and chirimoya. Naturally wheat-free, and the fruit does the work.</t>
+        </is>
+      </c>
+      <c r="G160" s="27" t="inlineStr">
+        <is>
+          <t>Plated</t>
+        </is>
+      </c>
+      <c r="H160" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I160" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J160" s="27" t="inlineStr">
+        <is>
+          <t>Huevo, azucar, crema, chirimoya</t>
+        </is>
+      </c>
+      <c r="K160" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L160" s="28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M160" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N160" s="30">
+        <f>IFERROR(L160/M160,"")</f>
+        <v/>
+      </c>
+      <c r="O160" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P160" s="31">
+        <f>IF(N160="","",IF(N160&gt;0.32,"Reprice or resource",IF(N160&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="27" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="27" t="inlineStr">
+        <is>
+          <t>Banana &amp; Chancaca Loaf</t>
+        </is>
+      </c>
+      <c r="C161" s="27" t="inlineStr">
+        <is>
+          <t>Banana bread</t>
+        </is>
+      </c>
+      <c r="D161" s="27" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E161" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F161" s="27" t="inlineStr">
+        <is>
+          <t>Chancaca instead of brown sugar, and a chancaca glaze while warm.</t>
+        </is>
+      </c>
+      <c r="G161" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H161" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I161" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J161" s="27" t="inlineStr">
+        <is>
+          <t>Platano, chancaca, harina, mantequilla</t>
+        </is>
+      </c>
+      <c r="K161" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L161" s="28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M161" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N161" s="30">
+        <f>IFERROR(L161/M161,"")</f>
+        <v/>
+      </c>
+      <c r="O161" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P161" s="31">
+        <f>IF(N161="","",IF(N161&gt;0.32,"Reprice or resource",IF(N161&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="27" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="27" t="inlineStr">
+        <is>
+          <t>Maracuya Curd Cake</t>
+        </is>
+      </c>
+      <c r="C162" s="27" t="inlineStr">
+        <is>
+          <t>Lemon curd cake</t>
+        </is>
+      </c>
+      <c r="D162" s="27" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E162" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F162" s="27" t="inlineStr">
+        <is>
+          <t>Maracuya where a Scottish bakery would use lemon. Sharper, and it holds colour in the box.</t>
+        </is>
+      </c>
+      <c r="G162" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H162" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I162" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J162" s="27" t="inlineStr">
+        <is>
+          <t>Maracuya, huevo, harina, mantequilla</t>
+        </is>
+      </c>
+      <c r="K162" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L162" s="28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M162" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="N162" s="30">
+        <f>IFERROR(L162/M162,"")</f>
+        <v/>
+      </c>
+      <c r="O162" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P162" s="31">
+        <f>IF(N162="","",IF(N162&gt;0.32,"Reprice or resource",IF(N162&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="27" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="27" t="inlineStr">
+        <is>
+          <t>Sticky Ginger Parkin</t>
+        </is>
+      </c>
+      <c r="C163" s="27" t="inlineStr">
+        <is>
+          <t>Parkin</t>
+        </is>
+      </c>
+      <c r="D163" s="27" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E163" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F163" s="27" t="inlineStr">
+        <is>
+          <t>The Yorkshire oat-and-treacle cake, chancaca for the treacle. Improves for a week in the tin.</t>
+        </is>
+      </c>
+      <c r="G163" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H163" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I163" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J163" s="27" t="inlineStr">
+        <is>
+          <t>Avena, chancaca, jengibre, harina</t>
+        </is>
+      </c>
+      <c r="K163" s="27" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="L163" s="28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M163" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N163" s="30">
+        <f>IFERROR(L163/M163,"")</f>
+        <v/>
+      </c>
+      <c r="O163" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P163" s="31">
+        <f>IF(N163="","",IF(N163&gt;0.32,"Reprice or resource",IF(N163&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="27" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="27" t="inlineStr">
+        <is>
+          <t>Aguaymanto Crumble Cake (vegan)</t>
+        </is>
+      </c>
+      <c r="C164" s="27" t="inlineStr">
+        <is>
+          <t>Crumble cake</t>
+        </is>
+      </c>
+      <c r="D164" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E164" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F164" s="27" t="inlineStr">
+        <is>
+          <t>Oil-based sponge, aguaymanto layer, oat crumble on top. Vegan and nobody has to be told.</t>
+        </is>
+      </c>
+      <c r="G164" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H164" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I164" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J164" s="27" t="inlineStr">
+        <is>
+          <t>Aguaymanto, avena, harina, aceite</t>
+        </is>
+      </c>
+      <c r="K164" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L164" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M164" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N164" s="30">
+        <f>IFERROR(L164/M164,"")</f>
+        <v/>
+      </c>
+      <c r="O164" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P164" s="31">
+        <f>IF(N164="","",IF(N164&gt;0.32,"Reprice or resource",IF(N164&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="27" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="27" t="inlineStr">
+        <is>
+          <t>Lemon &amp; Muna Drizzle Cake</t>
+        </is>
+      </c>
+      <c r="C165" s="27" t="inlineStr">
+        <is>
+          <t>Lemon drizzle</t>
+        </is>
+      </c>
+      <c r="D165" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E165" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F165" s="27" t="inlineStr">
+        <is>
+          <t>Muna in the syrup alongside the lemon - the Andean mint reads as something between mint and thyme.</t>
+        </is>
+      </c>
+      <c r="G165" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H165" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I165" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J165" s="27" t="inlineStr">
+        <is>
+          <t>Limon, muna, harina, mantequilla</t>
+        </is>
+      </c>
+      <c r="K165" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L165" s="28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M165" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N165" s="30">
+        <f>IFERROR(L165/M165,"")</f>
+        <v/>
+      </c>
+      <c r="O165" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P165" s="31">
+        <f>IF(N165="","",IF(N165&gt;0.32,"Reprice or resource",IF(N165&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="27" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="27" t="inlineStr">
+        <is>
+          <t>Papa Amarilla Chocolate Cake</t>
+        </is>
+      </c>
+      <c r="C166" s="27" t="inlineStr">
+        <is>
+          <t>Potato chocolate cake</t>
+        </is>
+      </c>
+      <c r="D166" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E166" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F166" s="27" t="inlineStr">
+        <is>
+          <t>Yellow potato in the crumb, no wheat. The same trick as the Scottish macaroon, made into a cake.</t>
+        </is>
+      </c>
+      <c r="G166" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H166" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I166" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J166" s="27" t="inlineStr">
+        <is>
+          <t>Papa amarilla, cacao, huevo, azucar</t>
+        </is>
+      </c>
+      <c r="K166" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; cacao distributor</t>
+        </is>
+      </c>
+      <c r="L166" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M166" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="N166" s="30">
+        <f>IFERROR(L166/M166,"")</f>
+        <v/>
+      </c>
+      <c r="O166" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P166" s="31">
+        <f>IF(N166="","",IF(N166&gt;0.32,"Reprice or resource",IF(N166&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="27" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="27" t="inlineStr">
+        <is>
+          <t>Tarta de Chirimoya y Crema</t>
+        </is>
+      </c>
+      <c r="C167" s="27" t="inlineStr">
+        <is>
+          <t>Cream tart</t>
+        </is>
+      </c>
+      <c r="D167" s="27" t="inlineStr">
+        <is>
+          <t>Basque</t>
+        </is>
+      </c>
+      <c r="E167" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F167" s="27" t="inlineStr">
+        <is>
+          <t>Chirimoya folded through set cream on a cacao base. Cold set, no oven on the day.</t>
+        </is>
+      </c>
+      <c r="G167" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H167" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I167" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J167" s="27" t="inlineStr">
+        <is>
+          <t>Chirimoya, crema, cacao, gelatina</t>
+        </is>
+      </c>
+      <c r="K167" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L167" s="28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M167" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="N167" s="30">
+        <f>IFERROR(L167/M167,"")</f>
+        <v/>
+      </c>
+      <c r="O167" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P167" s="31">
+        <f>IF(N167="","",IF(N167&gt;0.32,"Reprice or resource",IF(N167&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="27" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="27" t="inlineStr">
+        <is>
+          <t>Coconut &amp; Lucuma Traybake (vegan)</t>
+        </is>
+      </c>
+      <c r="C168" s="27" t="inlineStr">
+        <is>
+          <t>Traybake</t>
+        </is>
+      </c>
+      <c r="D168" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E168" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F168" s="27" t="inlineStr">
+        <is>
+          <t>Coconut oil and coconut milk carry the lucuma. Vegan, dairy-free and it travels better than butter does.</t>
+        </is>
+      </c>
+      <c r="G168" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H168" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I168" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J168" s="27" t="inlineStr">
+        <is>
+          <t>Lucuma, coco, harina, aceite de coco</t>
+        </is>
+      </c>
+      <c r="K168" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L168" s="28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M168" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="N168" s="30">
+        <f>IFERROR(L168/M168,"")</f>
+        <v/>
+      </c>
+      <c r="O168" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P168" s="31">
+        <f>IF(N168="","",IF(N168&gt;0.32,"Reprice or resource",IF(N168&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="27" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="27" t="inlineStr">
+        <is>
+          <t>Whisky Truffle Torte</t>
+        </is>
+      </c>
+      <c r="C169" s="27" t="inlineStr">
+        <is>
+          <t>Chocolate truffle torte</t>
+        </is>
+      </c>
+      <c r="D169" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E169" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F169" s="27" t="inlineStr">
+        <is>
+          <t>Flourless: Peruvian cacao, butter, egg and whisky. Coeliac-safe and the richest thing on the sheet.</t>
+        </is>
+      </c>
+      <c r="G169" s="27" t="inlineStr">
+        <is>
+          <t>Plated</t>
+        </is>
+      </c>
+      <c r="H169" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I169" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J169" s="27" t="inlineStr">
+        <is>
+          <t>Cacao, mantequilla, huevo, whisky</t>
+        </is>
+      </c>
+      <c r="K169" s="27" t="inlineStr">
+        <is>
+          <t>Cacao distributor; Makro</t>
+        </is>
+      </c>
+      <c r="L169" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M169" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="N169" s="30">
+        <f>IFERROR(L169/M169,"")</f>
+        <v/>
+      </c>
+      <c r="O169" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P169" s="31">
+        <f>IF(N169="","",IF(N169&gt;0.32,"Reprice or resource",IF(N169&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="27" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="27" t="inlineStr">
+        <is>
+          <t>Pisco Sour Meringue Tart</t>
+        </is>
+      </c>
+      <c r="C170" s="27" t="inlineStr">
+        <is>
+          <t>Lemon meringue pie</t>
+        </is>
+      </c>
+      <c r="D170" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E170" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F170" s="27" t="inlineStr">
+        <is>
+          <t>Lime curd with pisco and a torched meringue - the cocktail as a tart, and the licence covers both.</t>
+        </is>
+      </c>
+      <c r="G170" s="27" t="inlineStr">
+        <is>
+          <t>Plated</t>
+        </is>
+      </c>
+      <c r="H170" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I170" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J170" s="27" t="inlineStr">
+        <is>
+          <t>Limon, pisco, huevo, azucar</t>
+        </is>
+      </c>
+      <c r="K170" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; Makro</t>
+        </is>
+      </c>
+      <c r="L170" s="28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M170" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N170" s="30">
+        <f>IFERROR(L170/M170,"")</f>
+        <v/>
+      </c>
+      <c r="O170" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P170" s="31">
+        <f>IF(N170="","",IF(N170&gt;0.32,"Reprice or resource",IF(N170&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="27" t="inlineStr">
+        <is>
+          <t>Kiwicha Honey Cake</t>
+        </is>
+      </c>
+      <c r="C171" s="27" t="inlineStr">
+        <is>
+          <t>Honey cake</t>
+        </is>
+      </c>
+      <c r="D171" s="27" t="inlineStr">
+        <is>
+          <t>Nordic</t>
+        </is>
+      </c>
+      <c r="E171" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F171" s="27" t="inlineStr">
+        <is>
+          <t>Layers of kiwicha sponge with algarrobina cream. The Nordic honey cake, built on Andean grain.</t>
+        </is>
+      </c>
+      <c r="G171" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H171" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I171" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J171" s="27" t="inlineStr">
+        <is>
+          <t>Kiwicha, algarrobina, crema, harina</t>
+        </is>
+      </c>
+      <c r="K171" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L171" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M171" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="N171" s="30">
+        <f>IFERROR(L171/M171,"")</f>
+        <v/>
+      </c>
+      <c r="O171" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P171" s="31">
+        <f>IF(N171="","",IF(N171&gt;0.32,"Reprice or resource",IF(N171&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="27" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="27" t="inlineStr">
+        <is>
+          <t>Clootie Dumpling, Chancaca</t>
+        </is>
+      </c>
+      <c r="C172" s="27" t="inlineStr">
+        <is>
+          <t>Clootie dumpling</t>
+        </is>
+      </c>
+      <c r="D172" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E172" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F172" s="27" t="inlineStr">
+        <is>
+          <t>Steamed in a cloth like the original; chancaca for the treacle and aguaymanto for the currants. Keeps a fortnight and slices cold.</t>
+        </is>
+      </c>
+      <c r="G172" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H172" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I172" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J172" s="27" t="inlineStr">
+        <is>
+          <t>Harina, avena, chancaca, aguaymanto</t>
+        </is>
+      </c>
+      <c r="K172" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L172" s="28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M172" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="N172" s="30">
+        <f>IFERROR(L172/M172,"")</f>
+        <v/>
+      </c>
+      <c r="O172" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P172" s="31">
+        <f>IF(N172="","",IF(N172&gt;0.32,"Reprice or resource",IF(N172&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -12012,7 +13539,7 @@
         </is>
       </c>
       <c r="B4" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"Scottish")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"Scottish")</f>
         <v/>
       </c>
       <c r="C4" s="32">
@@ -12034,7 +13561,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"Scottish (Glasgow)")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"Scottish (Glasgow)")</f>
         <v/>
       </c>
       <c r="C5" s="32">
@@ -12051,7 +13578,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"English")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"English")</f>
         <v/>
       </c>
       <c r="C6" s="32">
@@ -12073,7 +13600,7 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"Greek")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"Greek")</f>
         <v/>
       </c>
       <c r="C7" s="32">
@@ -12095,7 +13622,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"Nordic")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"Nordic")</f>
         <v/>
       </c>
       <c r="C8" s="32">
@@ -12117,7 +13644,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"Basque")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"Basque")</f>
         <v/>
       </c>
       <c r="C9" s="32">
@@ -12139,7 +13666,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"Peruvian")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"Peruvian")</f>
         <v/>
       </c>
       <c r="C10" s="32">
@@ -12156,7 +13683,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$151,"Disputed (Lake District / Scotland)")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$172,"Disputed (Lake District / Scotland)")</f>
         <v/>
       </c>
       <c r="C11" s="32">
@@ -12216,7 +13743,7 @@
         </is>
       </c>
       <c r="B16" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$151,"Drop-off")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$172,"Drop-off")</f>
         <v/>
       </c>
       <c r="C16" s="23" t="n"/>
@@ -12230,7 +13757,7 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$151,"Buffet")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$172,"Buffet")</f>
         <v/>
       </c>
       <c r="C17" s="23" t="n"/>
@@ -12244,7 +13771,7 @@
         </is>
       </c>
       <c r="B18" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$151,"Plated")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$172,"Plated")</f>
         <v/>
       </c>
       <c r="C18" s="23" t="n"/>
@@ -12258,7 +13785,7 @@
         </is>
       </c>
       <c r="B19" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$151,"Live station")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$172,"Live station")</f>
         <v/>
       </c>
       <c r="C19" s="23" t="n"/>
@@ -12279,7 +13806,7 @@
         </is>
       </c>
       <c r="B21" s="22">
-        <f>COUNTIF(Matrix!$H$2:$H$151,"No")</f>
+        <f>COUNTIF(Matrix!$H$2:$H$172,"No")</f>
         <v/>
       </c>
       <c r="C21" s="23" t="n"/>
@@ -12293,7 +13820,7 @@
         </is>
       </c>
       <c r="B22" s="22">
-        <f>COUNTIF(Matrix!$I$2:$I$151,"Yes")</f>
+        <f>COUNTIF(Matrix!$I$2:$I$172,"Yes")</f>
         <v/>
       </c>
       <c r="C22" s="23" t="n"/>
@@ -12314,7 +13841,7 @@
         </is>
       </c>
       <c r="B24" s="22">
-        <f>COUNTIF(Matrix!$O$2:$O$151,"No - estimate")</f>
+        <f>COUNTIF(Matrix!$O$2:$O$172,"No - estimate")</f>
         <v/>
       </c>
       <c r="C24" s="23" t="inlineStr">

--- a/data/ayesicena-matrix.xlsx
+++ b/data/ayesicena-matrix.xlsx
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P172"/>
+  <dimension ref="A1:P192"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="18" min="1" max="1"/>
@@ -13462,6 +13462,1486 @@
       </c>
       <c r="P172" s="31">
         <f>IF(N172="","",IF(N172&gt;0.32,"Reprice or resource",IF(N172&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="27" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="27" t="inlineStr">
+        <is>
+          <t>Papa Rellena, Haggis</t>
+        </is>
+      </c>
+      <c r="C173" s="27" t="inlineStr">
+        <is>
+          <t>Papa rellena</t>
+        </is>
+      </c>
+      <c r="D173" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E173" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F173" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: haggis inside the potato instead of the usual beef picadillo. Fried to order, and the shell is the same.</t>
+        </is>
+      </c>
+      <c r="G173" s="27" t="inlineStr">
+        <is>
+          <t>Live station</t>
+        </is>
+      </c>
+      <c r="H173" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I173" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J173" s="27" t="inlineStr">
+        <is>
+          <t>Papa amarilla, lamb offal, avena, aji panca</t>
+        </is>
+      </c>
+      <c r="K173" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; Mercado de Magdalena</t>
+        </is>
+      </c>
+      <c r="L173" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M173" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N173" s="30">
+        <f>IFERROR(L173/M173,"")</f>
+        <v/>
+      </c>
+      <c r="O173" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P173" s="31">
+        <f>IF(N173="","",IF(N173&gt;0.32,"Reprice or resource",IF(N173&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="27" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="27" t="inlineStr">
+        <is>
+          <t>Tequenos de Paria y Whisky</t>
+        </is>
+      </c>
+      <c r="C174" s="27" t="inlineStr">
+        <is>
+          <t>Tequenos</t>
+        </is>
+      </c>
+      <c r="D174" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E174" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F174" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: queso paria in the wonton with a whisky and chancaca dip rather than guacamole.</t>
+        </is>
+      </c>
+      <c r="G174" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H174" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I174" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J174" s="27" t="inlineStr">
+        <is>
+          <t>Queso paria, masa wonton, whisky, chancaca</t>
+        </is>
+      </c>
+      <c r="K174" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L174" s="28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M174" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N174" s="30">
+        <f>IFERROR(L174/M174,"")</f>
+        <v/>
+      </c>
+      <c r="O174" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P174" s="31">
+        <f>IF(N174="","",IF(N174&gt;0.32,"Reprice or resource",IF(N174&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="27" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="27" t="inlineStr">
+        <is>
+          <t>Choclo con Queso, Mostaza</t>
+        </is>
+      </c>
+      <c r="C175" s="27" t="inlineStr">
+        <is>
+          <t>Choclo con queso</t>
+        </is>
+      </c>
+      <c r="D175" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E175" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F175" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: the street-corner choclo with a wholegrain mustard butter melted over it.</t>
+        </is>
+      </c>
+      <c r="G175" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H175" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I175" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J175" s="27" t="inlineStr">
+        <is>
+          <t>Choclo, queso fresco, mantequilla, mostaza</t>
+        </is>
+      </c>
+      <c r="K175" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L175" s="28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M175" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N175" s="30">
+        <f>IFERROR(L175/M175,"")</f>
+        <v/>
+      </c>
+      <c r="O175" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P175" s="31">
+        <f>IF(N175="","",IF(N175&gt;0.32,"Reprice or resource",IF(N175&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="27" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="27" t="inlineStr">
+        <is>
+          <t>Solterito de Quinua y Berros</t>
+        </is>
+      </c>
+      <c r="C176" s="27" t="inlineStr">
+        <is>
+          <t>Solterito</t>
+        </is>
+      </c>
+      <c r="D176" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E176" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F176" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: watercress carries the Arequipa salad where the habas run out. Vegan as built.</t>
+        </is>
+      </c>
+      <c r="G176" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H176" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I176" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J176" s="27" t="inlineStr">
+        <is>
+          <t>Quinua, berros, aceituna de Tacna, rocoto</t>
+        </is>
+      </c>
+      <c r="K176" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L176" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M176" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N176" s="30">
+        <f>IFERROR(L176/M176,"")</f>
+        <v/>
+      </c>
+      <c r="O176" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P176" s="31">
+        <f>IF(N176="","",IF(N176&gt;0.32,"Reprice or resource",IF(N176&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="27" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="27" t="inlineStr">
+        <is>
+          <t>Cau Cau de Setas</t>
+        </is>
+      </c>
+      <c r="C177" s="27" t="inlineStr">
+        <is>
+          <t>Cau cau</t>
+        </is>
+      </c>
+      <c r="D177" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E177" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F177" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: mushrooms instead of tripe, oats to thicken instead of potato alone. Vegan, and it does not read as a compromise.</t>
+        </is>
+      </c>
+      <c r="G177" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H177" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I177" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J177" s="27" t="inlineStr">
+        <is>
+          <t>Champinones, papa amarilla, aji amarillo, hierbabuena, avena</t>
+        </is>
+      </c>
+      <c r="K177" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L177" s="28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M177" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="N177" s="30">
+        <f>IFERROR(L177/M177,"")</f>
+        <v/>
+      </c>
+      <c r="O177" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P177" s="31">
+        <f>IF(N177="","",IF(N177&gt;0.32,"Reprice or resource",IF(N177&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="27" t="inlineStr">
+        <is>
+          <t>Seco de Cordero, Stout</t>
+        </is>
+      </c>
+      <c r="C178" s="27" t="inlineStr">
+        <is>
+          <t>Seco de cordero</t>
+        </is>
+      </c>
+      <c r="D178" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E178" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F178" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: stout in the braise where chicha de jora usually goes. Culantro stays; it is the whole dish.</t>
+        </is>
+      </c>
+      <c r="G178" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H178" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I178" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J178" s="27" t="inlineStr">
+        <is>
+          <t>Cordero, culantro, cerveza negra, frejol</t>
+        </is>
+      </c>
+      <c r="K178" s="27" t="inlineStr">
+        <is>
+          <t>Artisanal butcher; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L178" s="28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M178" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="N178" s="30">
+        <f>IFERROR(L178/M178,"")</f>
+        <v/>
+      </c>
+      <c r="O178" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P178" s="31">
+        <f>IF(N178="","",IF(N178&gt;0.32,"Reprice or resource",IF(N178&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="27" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="27" t="inlineStr">
+        <is>
+          <t>Adobo Arequipeno, Ale</t>
+        </is>
+      </c>
+      <c r="C179" s="27" t="inlineStr">
+        <is>
+          <t>Adobo arequipeno</t>
+        </is>
+      </c>
+      <c r="D179" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E179" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F179" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: Scotch ale in place of the chicha. A Sunday-morning dish sold as a Sunday-lunch centrepiece.</t>
+        </is>
+      </c>
+      <c r="G179" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H179" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I179" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J179" s="27" t="inlineStr">
+        <is>
+          <t>Cerdo, aji panca, cerveza, rocoto</t>
+        </is>
+      </c>
+      <c r="K179" s="27" t="inlineStr">
+        <is>
+          <t>Artisanal butcher; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L179" s="28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M179" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="N179" s="30">
+        <f>IFERROR(L179/M179,"")</f>
+        <v/>
+      </c>
+      <c r="O179" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P179" s="31">
+        <f>IF(N179="","",IF(N179&gt;0.32,"Reprice or resource",IF(N179&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="27" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="27" t="inlineStr">
+        <is>
+          <t>Tacu Tacu con Morcilla</t>
+        </is>
+      </c>
+      <c r="C180" s="27" t="inlineStr">
+        <is>
+          <t>Tacu tacu</t>
+        </is>
+      </c>
+      <c r="D180" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E180" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F180" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: morcilla folded through the rice and bean cake and crisped in the same pan.</t>
+        </is>
+      </c>
+      <c r="G180" s="27" t="inlineStr">
+        <is>
+          <t>Live station</t>
+        </is>
+      </c>
+      <c r="H180" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I180" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J180" s="27" t="inlineStr">
+        <is>
+          <t>Arroz, frejol, morcilla, aji amarillo</t>
+        </is>
+      </c>
+      <c r="K180" s="27" t="inlineStr">
+        <is>
+          <t>Makro; artisanal butcher</t>
+        </is>
+      </c>
+      <c r="L180" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="M180" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="N180" s="30">
+        <f>IFERROR(L180/M180,"")</f>
+        <v/>
+      </c>
+      <c r="O180" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P180" s="31">
+        <f>IF(N180="","",IF(N180&gt;0.32,"Reprice or resource",IF(N180&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="27" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="27" t="inlineStr">
+        <is>
+          <t>Sopa Criolla con Avena</t>
+        </is>
+      </c>
+      <c r="C181" s="27" t="inlineStr">
+        <is>
+          <t>Sopa criolla</t>
+        </is>
+      </c>
+      <c r="D181" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E181" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F181" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: pinhead oats carry the body where the noodles usually do. Faster and it holds far better.</t>
+        </is>
+      </c>
+      <c r="G181" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H181" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I181" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J181" s="27" t="inlineStr">
+        <is>
+          <t>Carne, avena, leche, aji panca, huevo</t>
+        </is>
+      </c>
+      <c r="K181" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L181" s="28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M181" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="N181" s="30">
+        <f>IFERROR(L181/M181,"")</f>
+        <v/>
+      </c>
+      <c r="O181" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P181" s="31">
+        <f>IF(N181="","",IF(N181&gt;0.32,"Reprice or resource",IF(N181&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="27" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="27" t="inlineStr">
+        <is>
+          <t>Chupe de Zapallo Loche</t>
+        </is>
+      </c>
+      <c r="C182" s="27" t="inlineStr">
+        <is>
+          <t>Chupe</t>
+        </is>
+      </c>
+      <c r="D182" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E182" s="27" t="inlineStr">
+        <is>
+          <t>Bowl</t>
+        </is>
+      </c>
+      <c r="F182" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: squash chupe finished with toasted oatmeal instead of cheese and egg. Vegan and it still eats rich.</t>
+        </is>
+      </c>
+      <c r="G182" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H182" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I182" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J182" s="27" t="inlineStr">
+        <is>
+          <t>Zapallo loche, papa amarilla, avena, huacatay</t>
+        </is>
+      </c>
+      <c r="K182" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L182" s="28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M182" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="N182" s="30">
+        <f>IFERROR(L182/M182,"")</f>
+        <v/>
+      </c>
+      <c r="O182" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P182" s="31">
+        <f>IF(N182="","",IF(N182&gt;0.32,"Reprice or resource",IF(N182&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="27" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="27" t="inlineStr">
+        <is>
+          <t>Ensalada de Palta y Berros</t>
+        </is>
+      </c>
+      <c r="C183" s="27" t="inlineStr">
+        <is>
+          <t>Ensalada de palta</t>
+        </is>
+      </c>
+      <c r="D183" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E183" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F183" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: watercress and a mustard-lime dressing under the avocado. Vegan, and the cheapest green on the sheet.</t>
+        </is>
+      </c>
+      <c r="G183" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H183" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I183" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J183" s="27" t="inlineStr">
+        <is>
+          <t>Palta, berros, limon, mostaza</t>
+        </is>
+      </c>
+      <c r="K183" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L183" s="28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M183" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N183" s="30">
+        <f>IFERROR(L183/M183,"")</f>
+        <v/>
+      </c>
+      <c r="O183" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P183" s="31">
+        <f>IF(N183="","",IF(N183&gt;0.32,"Reprice or resource",IF(N183&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="27" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="27" t="inlineStr">
+        <is>
+          <t>Huancaina Escocesa</t>
+        </is>
+      </c>
+      <c r="C184" s="27" t="inlineStr">
+        <is>
+          <t>Papa a la huancaina</t>
+        </is>
+      </c>
+      <c r="D184" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E184" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F184" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: mature cheddar carries the sauce alongside the queso fresco. Sharper, and it sets firmer for a buffet.</t>
+        </is>
+      </c>
+      <c r="G184" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H184" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I184" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J184" s="27" t="inlineStr">
+        <is>
+          <t>Papa amarilla, aji amarillo, queso cheddar, leche</t>
+        </is>
+      </c>
+      <c r="K184" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; Makro</t>
+        </is>
+      </c>
+      <c r="L184" s="28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M184" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="N184" s="30">
+        <f>IFERROR(L184/M184,"")</f>
+        <v/>
+      </c>
+      <c r="O184" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P184" s="31">
+        <f>IF(N184="","",IF(N184&gt;0.32,"Reprice or resource",IF(N184&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="27" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="27" t="inlineStr">
+        <is>
+          <t>Yuca Frita, Huancaina de Muna</t>
+        </is>
+      </c>
+      <c r="C185" s="27" t="inlineStr">
+        <is>
+          <t>Yuca frita</t>
+        </is>
+      </c>
+      <c r="D185" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E185" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F185" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: muna in the huancaina, which pushes it towards a herb sauce rather than a cheese one.</t>
+        </is>
+      </c>
+      <c r="G185" s="27" t="inlineStr">
+        <is>
+          <t>Live station</t>
+        </is>
+      </c>
+      <c r="H185" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I185" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J185" s="27" t="inlineStr">
+        <is>
+          <t>Yuca, aji amarillo, muna, queso fresco</t>
+        </is>
+      </c>
+      <c r="K185" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L185" s="28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M185" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N185" s="30">
+        <f>IFERROR(L185/M185,"")</f>
+        <v/>
+      </c>
+      <c r="O185" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P185" s="31">
+        <f>IF(N185="","",IF(N185&gt;0.32,"Reprice or resource",IF(N185&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="27" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="27" t="inlineStr">
+        <is>
+          <t>Anticucho de Champinon</t>
+        </is>
+      </c>
+      <c r="C186" s="27" t="inlineStr">
+        <is>
+          <t>Anticucho</t>
+        </is>
+      </c>
+      <c r="D186" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E186" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F186" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: field mushrooms in the panca marinade with muna. Vegan, and it outsells the beef heart with a mixed table.</t>
+        </is>
+      </c>
+      <c r="G186" s="27" t="inlineStr">
+        <is>
+          <t>Live station</t>
+        </is>
+      </c>
+      <c r="H186" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I186" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J186" s="27" t="inlineStr">
+        <is>
+          <t>Champinones, aji panca, muna, vinagre</t>
+        </is>
+      </c>
+      <c r="K186" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L186" s="28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M186" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N186" s="30">
+        <f>IFERROR(L186/M186,"")</f>
+        <v/>
+      </c>
+      <c r="O186" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P186" s="31">
+        <f>IF(N186="","",IF(N186&gt;0.32,"Reprice or resource",IF(N186&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="27" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="27" t="inlineStr">
+        <is>
+          <t>Empanada de Lomo Saltado</t>
+        </is>
+      </c>
+      <c r="C187" s="27" t="inlineStr">
+        <is>
+          <t>Empanada</t>
+        </is>
+      </c>
+      <c r="D187" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E187" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F187" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: the saltado goes into a bridie-style shortcrust rather than the usual empanada dough.</t>
+        </is>
+      </c>
+      <c r="G187" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H187" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I187" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J187" s="27" t="inlineStr">
+        <is>
+          <t>Lomo, cebolla, tomate, sillao, harina</t>
+        </is>
+      </c>
+      <c r="K187" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L187" s="28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M187" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N187" s="30">
+        <f>IFERROR(L187/M187,"")</f>
+        <v/>
+      </c>
+      <c r="O187" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P187" s="31">
+        <f>IF(N187="","",IF(N187&gt;0.32,"Reprice or resource",IF(N187&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="27" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="27" t="inlineStr">
+        <is>
+          <t>Pan Chuta, Mantequilla de Muna</t>
+        </is>
+      </c>
+      <c r="C188" s="27" t="inlineStr">
+        <is>
+          <t>Pan chuta</t>
+        </is>
+      </c>
+      <c r="D188" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E188" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F188" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: the Cusco bread served the way a Scottish table serves a bannock, with a whipped herb butter.</t>
+        </is>
+      </c>
+      <c r="G188" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H188" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I188" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J188" s="27" t="inlineStr">
+        <is>
+          <t>Harina, anis, muna, mantequilla</t>
+        </is>
+      </c>
+      <c r="K188" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L188" s="28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M188" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="N188" s="30">
+        <f>IFERROR(L188/M188,"")</f>
+        <v/>
+      </c>
+      <c r="O188" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P188" s="31">
+        <f>IF(N188="","",IF(N188&gt;0.32,"Reprice or resource",IF(N188&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="27" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="27" t="inlineStr">
+        <is>
+          <t>Mazamorra Morada, Oat Crumble</t>
+        </is>
+      </c>
+      <c r="C189" s="27" t="inlineStr">
+        <is>
+          <t>Mazamorra morada</t>
+        </is>
+      </c>
+      <c r="D189" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E189" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F189" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: an oat crumble scattered over at the last second. Vegan, and the crumble is what stops it being one texture.</t>
+        </is>
+      </c>
+      <c r="G189" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H189" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I189" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J189" s="27" t="inlineStr">
+        <is>
+          <t>Maiz morado, membrillo, pina, avena</t>
+        </is>
+      </c>
+      <c r="K189" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L189" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M189" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N189" s="30">
+        <f>IFERROR(L189/M189,"")</f>
+        <v/>
+      </c>
+      <c r="O189" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P189" s="31">
+        <f>IF(N189="","",IF(N189&gt;0.32,"Reprice or resource",IF(N189&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="27" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="27" t="inlineStr">
+        <is>
+          <t>Arroz con Leche, Whisky</t>
+        </is>
+      </c>
+      <c r="C190" s="27" t="inlineStr">
+        <is>
+          <t>Arroz con leche</t>
+        </is>
+      </c>
+      <c r="D190" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E190" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F190" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: whisky and a burnt-sugar top. Served cold in pots, it is the easiest dessert here to scale.</t>
+        </is>
+      </c>
+      <c r="G190" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H190" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I190" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J190" s="27" t="inlineStr">
+        <is>
+          <t>Arroz, leche, canela, whisky</t>
+        </is>
+      </c>
+      <c r="K190" s="27" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="L190" s="28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M190" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N190" s="30">
+        <f>IFERROR(L190/M190,"")</f>
+        <v/>
+      </c>
+      <c r="O190" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P190" s="31">
+        <f>IF(N190="","",IF(N190&gt;0.32,"Reprice or resource",IF(N190&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="27" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="27" t="inlineStr">
+        <is>
+          <t>King Kong de Lucuma</t>
+        </is>
+      </c>
+      <c r="C191" s="27" t="inlineStr">
+        <is>
+          <t>King Kong</t>
+        </is>
+      </c>
+      <c r="D191" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E191" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F191" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: shortbread-proportion biscuit layers with lucuma manjar. Firmer than the Lambayeque original and it boxes.</t>
+        </is>
+      </c>
+      <c r="G191" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H191" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I191" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J191" s="27" t="inlineStr">
+        <is>
+          <t>Harina, mantequilla, manjar blanco, lucuma</t>
+        </is>
+      </c>
+      <c r="K191" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L191" s="28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M191" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="N191" s="30">
+        <f>IFERROR(L191/M191,"")</f>
+        <v/>
+      </c>
+      <c r="O191" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P191" s="31">
+        <f>IF(N191="","",IF(N191&gt;0.32,"Reprice or resource",IF(N191&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="27" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="27" t="inlineStr">
+        <is>
+          <t>Champus de Chirimoya</t>
+        </is>
+      </c>
+      <c r="C192" s="27" t="inlineStr">
+        <is>
+          <t>Champus</t>
+        </is>
+      </c>
+      <c r="D192" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E192" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F192" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: oats in the champus alongside the maiz morado. Vegan, served warm, and it is a winter product.</t>
+        </is>
+      </c>
+      <c r="G192" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H192" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I192" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J192" s="27" t="inlineStr">
+        <is>
+          <t>Maiz morado, chirimoya, membrillo, avena</t>
+        </is>
+      </c>
+      <c r="K192" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L192" s="28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M192" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N192" s="30">
+        <f>IFERROR(L192/M192,"")</f>
+        <v/>
+      </c>
+      <c r="O192" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P192" s="31">
+        <f>IF(N192="","",IF(N192&gt;0.32,"Reprice or resource",IF(N192&lt;0.2,"Check cost is realistic","OK")))</f>
         <v/>
       </c>
     </row>
@@ -13539,7 +15019,7 @@
         </is>
       </c>
       <c r="B4" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"Scottish")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"Scottish")</f>
         <v/>
       </c>
       <c r="C4" s="32">
@@ -13561,7 +15041,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"Scottish (Glasgow)")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"Scottish (Glasgow)")</f>
         <v/>
       </c>
       <c r="C5" s="32">
@@ -13578,7 +15058,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"English")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"English")</f>
         <v/>
       </c>
       <c r="C6" s="32">
@@ -13600,7 +15080,7 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"Greek")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"Greek")</f>
         <v/>
       </c>
       <c r="C7" s="32">
@@ -13622,7 +15102,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"Nordic")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"Nordic")</f>
         <v/>
       </c>
       <c r="C8" s="32">
@@ -13644,7 +15124,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"Basque")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"Basque")</f>
         <v/>
       </c>
       <c r="C9" s="32">
@@ -13666,7 +15146,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"Peruvian")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"Peruvian")</f>
         <v/>
       </c>
       <c r="C10" s="32">
@@ -13683,7 +15163,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$172,"Disputed (Lake District / Scotland)")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$192,"Disputed (Lake District / Scotland)")</f>
         <v/>
       </c>
       <c r="C11" s="32">
@@ -13743,7 +15223,7 @@
         </is>
       </c>
       <c r="B16" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$172,"Drop-off")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$192,"Drop-off")</f>
         <v/>
       </c>
       <c r="C16" s="23" t="n"/>
@@ -13757,7 +15237,7 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$172,"Buffet")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$192,"Buffet")</f>
         <v/>
       </c>
       <c r="C17" s="23" t="n"/>
@@ -13771,7 +15251,7 @@
         </is>
       </c>
       <c r="B18" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$172,"Plated")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$192,"Plated")</f>
         <v/>
       </c>
       <c r="C18" s="23" t="n"/>
@@ -13785,7 +15265,7 @@
         </is>
       </c>
       <c r="B19" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$172,"Live station")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$192,"Live station")</f>
         <v/>
       </c>
       <c r="C19" s="23" t="n"/>
@@ -13806,7 +15286,7 @@
         </is>
       </c>
       <c r="B21" s="22">
-        <f>COUNTIF(Matrix!$H$2:$H$172,"No")</f>
+        <f>COUNTIF(Matrix!$H$2:$H$192,"No")</f>
         <v/>
       </c>
       <c r="C21" s="23" t="n"/>
@@ -13820,7 +15300,7 @@
         </is>
       </c>
       <c r="B22" s="22">
-        <f>COUNTIF(Matrix!$I$2:$I$172,"Yes")</f>
+        <f>COUNTIF(Matrix!$I$2:$I$192,"Yes")</f>
         <v/>
       </c>
       <c r="C22" s="23" t="n"/>
@@ -13841,7 +15321,7 @@
         </is>
       </c>
       <c r="B24" s="22">
-        <f>COUNTIF(Matrix!$O$2:$O$172,"No - estimate")</f>
+        <f>COUNTIF(Matrix!$O$2:$O$192,"No - estimate")</f>
         <v/>
       </c>
       <c r="C24" s="23" t="inlineStr">

--- a/data/ayesicena-matrix.xlsx
+++ b/data/ayesicena-matrix.xlsx
@@ -142,7 +142,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -243,6 +243,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P192"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="18" min="1" max="1"/>
@@ -14942,6 +14943,2397 @@
       </c>
       <c r="P192" s="31">
         <f>IF(N192="","",IF(N192&gt;0.32,"Reprice or resource",IF(N192&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="27" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="27" t="inlineStr">
+        <is>
+          <t>Arbroath Smokie Pate, Rocoto</t>
+        </is>
+      </c>
+      <c r="C193" s="27" t="inlineStr">
+        <is>
+          <t>Arbroath smokie</t>
+        </is>
+      </c>
+      <c r="D193" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E193" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F193" s="27" t="inlineStr">
+        <is>
+          <t>Hot-smoked Andean trout stands in for the Arbroath smokie - the same hard smoke, from a fish that reaches Lima fresh. Rocoto in the butter is the heat the original never had.</t>
+        </is>
+      </c>
+      <c r="G193" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H193" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I193" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J193" s="27" t="inlineStr">
+        <is>
+          <t>Trucha ahumada, rocoto, mantequilla, limon</t>
+        </is>
+      </c>
+      <c r="K193" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L193" s="28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M193" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="N193" s="30">
+        <f>IFERROR(L193/M193,"")</f>
+        <v/>
+      </c>
+      <c r="O193" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P193" s="31">
+        <f>IF(N193="","",IF(N193&gt;0.32,"Reprice or resource",IF(N193&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="27" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="27" t="inlineStr">
+        <is>
+          <t>Partan Bree Shots</t>
+        </is>
+      </c>
+      <c r="C194" s="27" t="inlineStr">
+        <is>
+          <t>Partan bree</t>
+        </is>
+      </c>
+      <c r="D194" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E194" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F194" s="27" t="inlineStr">
+        <is>
+          <t>The Aberdeenshire crab soup poured into shot glasses, thickened with rice as the original is, and finished with choclo instead of croutons.</t>
+        </is>
+      </c>
+      <c r="G194" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H194" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I194" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J194" s="27" t="inlineStr">
+        <is>
+          <t>Cangrejo, arroz, choclo, leche</t>
+        </is>
+      </c>
+      <c r="K194" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero</t>
+        </is>
+      </c>
+      <c r="L194" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M194" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="N194" s="30">
+        <f>IFERROR(L194/M194,"")</f>
+        <v/>
+      </c>
+      <c r="O194" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P194" s="31">
+        <f>IF(N194="","",IF(N194&gt;0.32,"Reprice or resource",IF(N194&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="27" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="27" t="inlineStr">
+        <is>
+          <t>Skirlie Mushroom Caps</t>
+        </is>
+      </c>
+      <c r="C195" s="27" t="inlineStr">
+        <is>
+          <t>Skirlie</t>
+        </is>
+      </c>
+      <c r="D195" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E195" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F195" s="27" t="inlineStr">
+        <is>
+          <t>Quinoa skirlie packed into field mushrooms with aji amarillo. Vegetarian, and the toasted oats do the work the sausage meat would.</t>
+        </is>
+      </c>
+      <c r="G195" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H195" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I195" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J195" s="27" t="inlineStr">
+        <is>
+          <t>Champinones, quinua, aji amarillo, avena</t>
+        </is>
+      </c>
+      <c r="K195" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L195" s="28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M195" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N195" s="30">
+        <f>IFERROR(L195/M195,"")</f>
+        <v/>
+      </c>
+      <c r="O195" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P195" s="31">
+        <f>IF(N195="","",IF(N195&gt;0.32,"Reprice or resource",IF(N195&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="27" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="27" t="inlineStr">
+        <is>
+          <t>Venison &amp; Juniper Sausage Rolls</t>
+        </is>
+      </c>
+      <c r="C196" s="27" t="inlineStr">
+        <is>
+          <t>Venison sausage roll</t>
+        </is>
+      </c>
+      <c r="D196" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E196" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F196" s="27" t="inlineStr">
+        <is>
+          <t>Alpaca replaces the Highland venison - lean, dark, and the closest thing Peru raises to it. Juniper and a little pork fat keep it from drying out in the oven.</t>
+        </is>
+      </c>
+      <c r="G196" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H196" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I196" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J196" s="27" t="inlineStr">
+        <is>
+          <t>Alpaca, enebro, panceta, hojaldre</t>
+        </is>
+      </c>
+      <c r="K196" s="27" t="inlineStr">
+        <is>
+          <t>Mercado de Magdalena; Makro</t>
+        </is>
+      </c>
+      <c r="L196" s="28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M196" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N196" s="30">
+        <f>IFERROR(L196/M196,"")</f>
+        <v/>
+      </c>
+      <c r="O196" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P196" s="31">
+        <f>IF(N196="","",IF(N196&gt;0.32,"Reprice or resource",IF(N196&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="27" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="27" t="inlineStr">
+        <is>
+          <t>Musselburgh Pie Minis</t>
+        </is>
+      </c>
+      <c r="C197" s="27" t="inlineStr">
+        <is>
+          <t>Musselburgh pie</t>
+        </is>
+      </c>
+      <c r="D197" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E197" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F197" s="27" t="inlineStr">
+        <is>
+          <t>Steak and oyster in a raised crust; conchas de abanico take the oyster's place. The scallop veda closes it for part of the year, which the planner flags before it is quoted.</t>
+        </is>
+      </c>
+      <c r="G197" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H197" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I197" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J197" s="27" t="inlineStr">
+        <is>
+          <t>Asado de tira, conchas de abanico, cerveza negra</t>
+        </is>
+      </c>
+      <c r="K197" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero; Makro</t>
+        </is>
+      </c>
+      <c r="L197" s="28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M197" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="N197" s="30">
+        <f>IFERROR(L197/M197,"")</f>
+        <v/>
+      </c>
+      <c r="O197" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P197" s="31">
+        <f>IF(N197="","",IF(N197&gt;0.32,"Reprice or resource",IF(N197&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="27" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="27" t="inlineStr">
+        <is>
+          <t>Mealie Pudding Bites, Aji Amarillo</t>
+        </is>
+      </c>
+      <c r="C198" s="27" t="inlineStr">
+        <is>
+          <t>Mealie pudding</t>
+        </is>
+      </c>
+      <c r="D198" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E198" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F198" s="27" t="inlineStr">
+        <is>
+          <t>The oat pudding with no blood in it, rolled small and fried, with an aji amarillo dip. Cheapest piece on the canape list by a distance.</t>
+        </is>
+      </c>
+      <c r="G198" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H198" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I198" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J198" s="27" t="inlineStr">
+        <is>
+          <t>Avena, cebolla, sebo, aji amarillo</t>
+        </is>
+      </c>
+      <c r="K198" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L198" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M198" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N198" s="30">
+        <f>IFERROR(L198/M198,"")</f>
+        <v/>
+      </c>
+      <c r="O198" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P198" s="31">
+        <f>IF(N198="","",IF(N198&gt;0.32,"Reprice or resource",IF(N198&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="27" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="27" t="inlineStr">
+        <is>
+          <t>Haggis, Neeps &amp; Tatties</t>
+        </is>
+      </c>
+      <c r="C199" s="27" t="inlineStr">
+        <is>
+          <t>Haggis</t>
+        </is>
+      </c>
+      <c r="D199" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E199" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F199" s="27" t="inlineStr">
+        <is>
+          <t>The plate itself, unaltered in shape. Papa amarilla goes into the tatties and the whisky sauce carries chancaca, so the sweetness is Peruvian and the structure is not.</t>
+        </is>
+      </c>
+      <c r="G199" s="27" t="inlineStr">
+        <is>
+          <t>Plated</t>
+        </is>
+      </c>
+      <c r="H199" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I199" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J199" s="27" t="inlineStr">
+        <is>
+          <t>Haggis, nabo, papa amarilla, whisky</t>
+        </is>
+      </c>
+      <c r="K199" s="27" t="inlineStr">
+        <is>
+          <t>Mercado de Magdalena; Makro</t>
+        </is>
+      </c>
+      <c r="L199" s="28" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M199" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="N199" s="30">
+        <f>IFERROR(L199/M199,"")</f>
+        <v/>
+      </c>
+      <c r="O199" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P199" s="31">
+        <f>IF(N199="","",IF(N199&gt;0.32,"Reprice or resource",IF(N199&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="27" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="27" t="inlineStr">
+        <is>
+          <t>Vegetarian Haggis, Quinoa</t>
+        </is>
+      </c>
+      <c r="C200" s="27" t="inlineStr">
+        <is>
+          <t>Haggis</t>
+        </is>
+      </c>
+      <c r="D200" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E200" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F200" s="27" t="inlineStr">
+        <is>
+          <t>Quinoa, kiwicha, lentils and oats built to the same spice line as the meat haggis. It sells to more of the room than the original and costs half as much to make.</t>
+        </is>
+      </c>
+      <c r="G200" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H200" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I200" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J200" s="27" t="inlineStr">
+        <is>
+          <t>Quinua, kiwicha, avena, nabo</t>
+        </is>
+      </c>
+      <c r="K200" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; Makro</t>
+        </is>
+      </c>
+      <c r="L200" s="28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M200" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="N200" s="30">
+        <f>IFERROR(L200/M200,"")</f>
+        <v/>
+      </c>
+      <c r="O200" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P200" s="31">
+        <f>IF(N200="","",IF(N200&gt;0.32,"Reprice or resource",IF(N200&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="27" t="inlineStr">
+        <is>
+          <t>Beef Olives, Aji Panca</t>
+        </is>
+      </c>
+      <c r="C201" s="27" t="inlineStr">
+        <is>
+          <t>Beef olives</t>
+        </is>
+      </c>
+      <c r="D201" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E201" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F201" s="27" t="inlineStr">
+        <is>
+          <t>Thin beef rolled round an oat and onion stuffing and braised long. Aji panca in the braise turns the gravy a colour a Scottish butcher would recognise anyway.</t>
+        </is>
+      </c>
+      <c r="G201" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H201" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I201" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J201" s="27" t="inlineStr">
+        <is>
+          <t>Carne, avena, cebolla, aji panca</t>
+        </is>
+      </c>
+      <c r="K201" s="27" t="inlineStr">
+        <is>
+          <t>Mercado de Magdalena; Makro</t>
+        </is>
+      </c>
+      <c r="L201" s="28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M201" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="N201" s="30">
+        <f>IFERROR(L201/M201,"")</f>
+        <v/>
+      </c>
+      <c r="O201" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P201" s="31">
+        <f>IF(N201="","",IF(N201&gt;0.32,"Reprice or resource",IF(N201&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="27" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="27" t="inlineStr">
+        <is>
+          <t>Finnan Haddie, Mustard Cream</t>
+        </is>
+      </c>
+      <c r="C202" s="27" t="inlineStr">
+        <is>
+          <t>Finnan haddie</t>
+        </is>
+      </c>
+      <c r="D202" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E202" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F202" s="27" t="inlineStr">
+        <is>
+          <t>Cold-smoked haddock has no Lima equivalent, so corvina is smoked to order. Mustard cream and a wholegrain crust; the corvina veda closes it two months a year.</t>
+        </is>
+      </c>
+      <c r="G202" s="27" t="inlineStr">
+        <is>
+          <t>Plated</t>
+        </is>
+      </c>
+      <c r="H202" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I202" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J202" s="27" t="inlineStr">
+        <is>
+          <t>Corvina ahumada, mostaza, crema, papa</t>
+        </is>
+      </c>
+      <c r="K202" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero</t>
+        </is>
+      </c>
+      <c r="L202" s="28" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M202" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="N202" s="30">
+        <f>IFERROR(L202/M202,"")</f>
+        <v/>
+      </c>
+      <c r="O202" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P202" s="31">
+        <f>IF(N202="","",IF(N202&gt;0.32,"Reprice or resource",IF(N202&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="27" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="27" t="inlineStr">
+        <is>
+          <t>Whole Poached Salmon, Muna</t>
+        </is>
+      </c>
+      <c r="C203" s="27" t="inlineStr">
+        <is>
+          <t>Poached salmon</t>
+        </is>
+      </c>
+      <c r="D203" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E203" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F203" s="27" t="inlineStr">
+        <is>
+          <t>The centrepiece a Scottish wedding expects, poached in a court-bouillon with muna in place of dill and served cold with a huacatay mayonnaise.</t>
+        </is>
+      </c>
+      <c r="G203" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H203" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I203" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J203" s="27" t="inlineStr">
+        <is>
+          <t>Salmon, muna, huacatay, limon</t>
+        </is>
+      </c>
+      <c r="K203" s="27" t="inlineStr">
+        <is>
+          <t>Makro (importado)</t>
+        </is>
+      </c>
+      <c r="L203" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M203" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="N203" s="30">
+        <f>IFERROR(L203/M203,"")</f>
+        <v/>
+      </c>
+      <c r="O203" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P203" s="31">
+        <f>IF(N203="","",IF(N203&gt;0.32,"Reprice or resource",IF(N203&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="27" t="inlineStr">
+        <is>
+          <t>Venison &amp; Alpaca Pie, Juniper</t>
+        </is>
+      </c>
+      <c r="C204" s="27" t="inlineStr">
+        <is>
+          <t>Venison pie</t>
+        </is>
+      </c>
+      <c r="D204" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E204" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F204" s="27" t="inlineStr">
+        <is>
+          <t>Alpaca braised in stout with juniper under a suet crust - the leanest red meat in the country doing the job Highland venison does at home.</t>
+        </is>
+      </c>
+      <c r="G204" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H204" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I204" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J204" s="27" t="inlineStr">
+        <is>
+          <t>Alpaca, cerveza negra, enebro, sebo</t>
+        </is>
+      </c>
+      <c r="K204" s="27" t="inlineStr">
+        <is>
+          <t>Mercado de Magdalena; Makro</t>
+        </is>
+      </c>
+      <c r="L204" s="28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M204" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="N204" s="30">
+        <f>IFERROR(L204/M204,"")</f>
+        <v/>
+      </c>
+      <c r="O204" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P204" s="31">
+        <f>IF(N204="","",IF(N204&gt;0.32,"Reprice or resource",IF(N204&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="27" t="inlineStr">
+        <is>
+          <t>Smokie &amp; Choclo Fishcakes</t>
+        </is>
+      </c>
+      <c r="C205" s="27" t="inlineStr">
+        <is>
+          <t>Fishcake</t>
+        </is>
+      </c>
+      <c r="D205" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E205" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F205" s="27" t="inlineStr">
+        <is>
+          <t>Smoked trout and potato bound tight, crumbed in panko cut with choclo meal. The choclo makes the crust sweeter and coarser than a Scottish chip shop would.</t>
+        </is>
+      </c>
+      <c r="G205" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H205" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I205" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J205" s="27" t="inlineStr">
+        <is>
+          <t>Trucha ahumada, papa blanca, choclo, panko</t>
+        </is>
+      </c>
+      <c r="K205" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L205" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M205" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="N205" s="30">
+        <f>IFERROR(L205/M205,"")</f>
+        <v/>
+      </c>
+      <c r="O205" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P205" s="31">
+        <f>IF(N205="","",IF(N205&gt;0.32,"Reprice or resource",IF(N205&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="27" t="inlineStr">
+        <is>
+          <t>Bashed Neeps, Chancaca Butter</t>
+        </is>
+      </c>
+      <c r="C206" s="27" t="inlineStr">
+        <is>
+          <t>Bashed neeps</t>
+        </is>
+      </c>
+      <c r="D206" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E206" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F206" s="27" t="inlineStr">
+        <is>
+          <t>Turnip mashed hard with a chancaca butter stirred through at the end. The molasses note is what Scottish cooks reach for sugar and white pepper to get.</t>
+        </is>
+      </c>
+      <c r="G206" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H206" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I206" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J206" s="27" t="inlineStr">
+        <is>
+          <t>Nabo, chancaca, mantequilla, pimienta</t>
+        </is>
+      </c>
+      <c r="K206" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L206" s="28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M206" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N206" s="30">
+        <f>IFERROR(L206/M206,"")</f>
+        <v/>
+      </c>
+      <c r="O206" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P206" s="31">
+        <f>IF(N206="","",IF(N206&gt;0.32,"Reprice or resource",IF(N206&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="27" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="27" t="inlineStr">
+        <is>
+          <t>Kale &amp; Oat Crumb Gratin</t>
+        </is>
+      </c>
+      <c r="C207" s="27" t="inlineStr">
+        <is>
+          <t>Kale gratin</t>
+        </is>
+      </c>
+      <c r="D207" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E207" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F207" s="27" t="inlineStr">
+        <is>
+          <t>Kale under an oat and paria crumb, baked hard. It travels better than any creamed green and reheats without collapsing into water.</t>
+        </is>
+      </c>
+      <c r="G207" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H207" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I207" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J207" s="27" t="inlineStr">
+        <is>
+          <t>Kale, avena, queso paria, leche</t>
+        </is>
+      </c>
+      <c r="K207" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; Makro</t>
+        </is>
+      </c>
+      <c r="L207" s="28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M207" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N207" s="30">
+        <f>IFERROR(L207/M207,"")</f>
+        <v/>
+      </c>
+      <c r="O207" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P207" s="31">
+        <f>IF(N207="","",IF(N207&gt;0.32,"Reprice or resource",IF(N207&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="27" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="27" t="inlineStr">
+        <is>
+          <t>Ayrshire Potatoes, Huacatay Butter</t>
+        </is>
+      </c>
+      <c r="C208" s="27" t="inlineStr">
+        <is>
+          <t>New potatoes</t>
+        </is>
+      </c>
+      <c r="D208" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E208" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F208" s="27" t="inlineStr">
+        <is>
+          <t>Small waxy potatoes boiled in their skins and rolled in huacatay butter. Papa nativa gives them colours an Ayrshire crop never had.</t>
+        </is>
+      </c>
+      <c r="G208" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H208" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I208" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J208" s="27" t="inlineStr">
+        <is>
+          <t>Papa nativa, huacatay, mantequilla, sal de Maras</t>
+        </is>
+      </c>
+      <c r="K208" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L208" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M208" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="N208" s="30">
+        <f>IFERROR(L208/M208,"")</f>
+        <v/>
+      </c>
+      <c r="O208" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P208" s="31">
+        <f>IF(N208="","",IF(N208&gt;0.32,"Reprice or resource",IF(N208&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="27" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="27" t="inlineStr">
+        <is>
+          <t>Barley Bannocks, Muna Butter</t>
+        </is>
+      </c>
+      <c r="C209" s="27" t="inlineStr">
+        <is>
+          <t>Bannock</t>
+        </is>
+      </c>
+      <c r="D209" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E209" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F209" s="27" t="inlineStr">
+        <is>
+          <t>Griddled barley bannocks - the bread that predates the oven in Scotland - with a whipped muna butter. Warm they are a side; cold they are a canape base.</t>
+        </is>
+      </c>
+      <c r="G209" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H209" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I209" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J209" s="27" t="inlineStr">
+        <is>
+          <t>Cebada, harina, muna, mantequilla</t>
+        </is>
+      </c>
+      <c r="K209" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L209" s="28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M209" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N209" s="30">
+        <f>IFERROR(L209/M209,"")</f>
+        <v/>
+      </c>
+      <c r="O209" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P209" s="31">
+        <f>IF(N209="","",IF(N209&gt;0.32,"Reprice or resource",IF(N209&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="27" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="27" t="inlineStr">
+        <is>
+          <t>Partan Bree Bowl</t>
+        </is>
+      </c>
+      <c r="C210" s="27" t="inlineStr">
+        <is>
+          <t>Partan bree</t>
+        </is>
+      </c>
+      <c r="D210" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E210" s="27" t="inlineStr">
+        <is>
+          <t>Bowl</t>
+        </is>
+      </c>
+      <c r="F210" s="27" t="inlineStr">
+        <is>
+          <t>The crab soup at bowl size with the rice cooked into it, choclo and a rocoto oil. Rich enough to be lunch, and only sellable in a month the crab veda is open.</t>
+        </is>
+      </c>
+      <c r="G210" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H210" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I210" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J210" s="27" t="inlineStr">
+        <is>
+          <t>Cangrejo, arroz, choclo, rocoto</t>
+        </is>
+      </c>
+      <c r="K210" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero</t>
+        </is>
+      </c>
+      <c r="L210" s="28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M210" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="N210" s="30">
+        <f>IFERROR(L210/M210,"")</f>
+        <v/>
+      </c>
+      <c r="O210" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P210" s="31">
+        <f>IF(N210="","",IF(N210&gt;0.32,"Reprice or resource",IF(N210&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="27" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="27" t="inlineStr">
+        <is>
+          <t>Barley &amp; Kale Bowl, Aji Verde</t>
+        </is>
+      </c>
+      <c r="C211" s="27" t="inlineStr">
+        <is>
+          <t>Barley broth</t>
+        </is>
+      </c>
+      <c r="D211" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E211" s="27" t="inlineStr">
+        <is>
+          <t>Bowl</t>
+        </is>
+      </c>
+      <c r="F211" s="27" t="inlineStr">
+        <is>
+          <t>Pearl barley, kale and roast squash under an aji verde dressing. Vegan, cheap to build, and the barley is what keeps it eating like a Scottish bowl rather than a salad.</t>
+        </is>
+      </c>
+      <c r="G211" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H211" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I211" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J211" s="27" t="inlineStr">
+        <is>
+          <t>Cebada, kale, zapallo, aji amarillo</t>
+        </is>
+      </c>
+      <c r="K211" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L211" s="28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M211" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N211" s="30">
+        <f>IFERROR(L211/M211,"")</f>
+        <v/>
+      </c>
+      <c r="O211" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P211" s="31">
+        <f>IF(N211="","",IF(N211&gt;0.32,"Reprice or resource",IF(N211&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="27" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="27" t="inlineStr">
+        <is>
+          <t>Kippered Trout, Muna Butter</t>
+        </is>
+      </c>
+      <c r="C212" s="27" t="inlineStr">
+        <is>
+          <t>Kipper</t>
+        </is>
+      </c>
+      <c r="D212" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E212" s="27" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F212" s="27" t="inlineStr">
+        <is>
+          <t>A whole trout butterflied and hard-smoked the way a herring is kippered, then grilled to order under muna butter. The Lima fish that gets closest to a Loch Fyne kipper.</t>
+        </is>
+      </c>
+      <c r="G212" s="27" t="inlineStr">
+        <is>
+          <t>Live station</t>
+        </is>
+      </c>
+      <c r="H212" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I212" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J212" s="27" t="inlineStr">
+        <is>
+          <t>Trucha, muna, mantequilla, limon</t>
+        </is>
+      </c>
+      <c r="K212" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero</t>
+        </is>
+      </c>
+      <c r="L212" s="28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M212" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="N212" s="30">
+        <f>IFERROR(L212/M212,"")</f>
+        <v/>
+      </c>
+      <c r="O212" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P212" s="31">
+        <f>IF(N212="","",IF(N212&gt;0.32,"Reprice or resource",IF(N212&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="27" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="27" t="inlineStr">
+        <is>
+          <t>Aguaymanto Brose</t>
+        </is>
+      </c>
+      <c r="C213" s="27" t="inlineStr">
+        <is>
+          <t>Brose</t>
+        </is>
+      </c>
+      <c r="D213" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E213" s="27" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F213" s="27" t="inlineStr">
+        <is>
+          <t>Oatmeal soaked raw overnight rather than cooked - the older, plainer cousin of porridge - with aguaymanto and honey. Ready in the box, no heat needed at the venue.</t>
+        </is>
+      </c>
+      <c r="G213" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H213" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I213" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J213" s="27" t="inlineStr">
+        <is>
+          <t>Avena, aguaymanto, miel, leche</t>
+        </is>
+      </c>
+      <c r="K213" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L213" s="28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M213" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N213" s="30">
+        <f>IFERROR(L213/M213,"")</f>
+        <v/>
+      </c>
+      <c r="O213" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P213" s="31">
+        <f>IF(N213="","",IF(N213&gt;0.32,"Reprice or resource",IF(N213&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="27" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="27" t="inlineStr">
+        <is>
+          <t>Cranachan Overnight Oats</t>
+        </is>
+      </c>
+      <c r="C214" s="27" t="inlineStr">
+        <is>
+          <t>Cranachan</t>
+        </is>
+      </c>
+      <c r="D214" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E214" s="27" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="F214" s="27" t="inlineStr">
+        <is>
+          <t>Cranachan taken off the dessert list and sold as breakfast: oats, cream, honey and chirimoya, with the whisky left out. Same build, different hour.</t>
+        </is>
+      </c>
+      <c r="G214" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H214" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I214" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J214" s="27" t="inlineStr">
+        <is>
+          <t>Avena, crema, miel, chirimoya</t>
+        </is>
+      </c>
+      <c r="K214" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1; Makro</t>
+        </is>
+      </c>
+      <c r="L214" s="28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M214" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N214" s="30">
+        <f>IFERROR(L214/M214,"")</f>
+        <v/>
+      </c>
+      <c r="O214" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P214" s="31">
+        <f>IF(N214="","",IF(N214&gt;0.32,"Reprice or resource",IF(N214&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="27" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="27" t="inlineStr">
+        <is>
+          <t>Malt Whisky Ice Cream, Chancaca</t>
+        </is>
+      </c>
+      <c r="C215" s="27" t="inlineStr">
+        <is>
+          <t>Ice cream</t>
+        </is>
+      </c>
+      <c r="D215" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E215" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F215" s="27" t="inlineStr">
+        <is>
+          <t>A custard ice cream with single malt folded in late so it stays soft, over a warm chancaca sauce. The only frozen product on the list, and the one that needs a freezer plan.</t>
+        </is>
+      </c>
+      <c r="G215" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H215" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I215" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J215" s="27" t="inlineStr">
+        <is>
+          <t>Crema, huevo, whisky, chancaca</t>
+        </is>
+      </c>
+      <c r="K215" s="27" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="L215" s="28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M215" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="N215" s="30">
+        <f>IFERROR(L215/M215,"")</f>
+        <v/>
+      </c>
+      <c r="O215" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P215" s="31">
+        <f>IF(N215="","",IF(N215&gt;0.32,"Reprice or resource",IF(N215&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="27" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="27" t="inlineStr">
+        <is>
+          <t>Dundee Marmalade Pudding</t>
+        </is>
+      </c>
+      <c r="C216" s="27" t="inlineStr">
+        <is>
+          <t>Marmalade pudding</t>
+        </is>
+      </c>
+      <c r="D216" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E216" s="27" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="F216" s="27" t="inlineStr">
+        <is>
+          <t>A steamed sponge with Dundee marmalade in the base, the marmalade cut with naranja agria. It steams ahead and reheats better than any plated dessert here.</t>
+        </is>
+      </c>
+      <c r="G216" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H216" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I216" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J216" s="27" t="inlineStr">
+        <is>
+          <t>Mermelada, naranja agria, harina, mantequilla</t>
+        </is>
+      </c>
+      <c r="K216" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L216" s="28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M216" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N216" s="30">
+        <f>IFERROR(L216/M216,"")</f>
+        <v/>
+      </c>
+      <c r="O216" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P216" s="31">
+        <f>IF(N216="","",IF(N216&gt;0.32,"Reprice or resource",IF(N216&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="27" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="27" t="inlineStr">
+        <is>
+          <t>Abernethy Biscuits, Anise</t>
+        </is>
+      </c>
+      <c r="C217" s="27" t="inlineStr">
+        <is>
+          <t>Abernethy biscuit</t>
+        </is>
+      </c>
+      <c r="D217" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E217" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F217" s="27" t="inlineStr">
+        <is>
+          <t>The plain caraway biscuit from Abernethy, rebuilt with anise - the seed a Peruvian bakery actually stocks, and the one already in pan chuta.</t>
+        </is>
+      </c>
+      <c r="G217" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H217" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I217" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J217" s="27" t="inlineStr">
+        <is>
+          <t>Harina, mantequilla, anis, azucar</t>
+        </is>
+      </c>
+      <c r="K217" s="27" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="L217" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M217" s="29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N217" s="30">
+        <f>IFERROR(L217/M217,"")</f>
+        <v/>
+      </c>
+      <c r="O217" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P217" s="31">
+        <f>IF(N217="","",IF(N217&gt;0.32,"Reprice or resource",IF(N217&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="27" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="27" t="inlineStr">
+        <is>
+          <t>Paris Bun, Chancaca Sugar</t>
+        </is>
+      </c>
+      <c r="C218" s="27" t="inlineStr">
+        <is>
+          <t>Paris bun</t>
+        </is>
+      </c>
+      <c r="D218" s="27" t="inlineStr">
+        <is>
+          <t>Scottish</t>
+        </is>
+      </c>
+      <c r="E218" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F218" s="27" t="inlineStr">
+        <is>
+          <t>The flat sugared bun from every Scottish baker's window, topped with chancaca sugar instead of nibbed white. Cheap, sweet, and it sells to children first.</t>
+        </is>
+      </c>
+      <c r="G218" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H218" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I218" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J218" s="27" t="inlineStr">
+        <is>
+          <t>Harina, mantequilla, chancaca, huevo</t>
+        </is>
+      </c>
+      <c r="K218" s="27" t="inlineStr">
+        <is>
+          <t>Makro</t>
+        </is>
+      </c>
+      <c r="L218" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M218" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N218" s="30">
+        <f>IFERROR(L218/M218,"")</f>
+        <v/>
+      </c>
+      <c r="O218" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P218" s="31">
+        <f>IF(N218="","",IF(N218&gt;0.32,"Reprice or resource",IF(N218&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="27" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="27" t="inlineStr">
+        <is>
+          <t>Sopa a la Minuta con Cebada</t>
+        </is>
+      </c>
+      <c r="C219" s="27" t="inlineStr">
+        <is>
+          <t>Sopa a la minuta</t>
+        </is>
+      </c>
+      <c r="D219" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E219" s="27" t="inlineStr">
+        <is>
+          <t>Bowl</t>
+        </is>
+      </c>
+      <c r="F219" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: pearl barley in place of the fideo, which turns Lima's fastest soup into something much closer to a Scotch broth.</t>
+        </is>
+      </c>
+      <c r="G219" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H219" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I219" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J219" s="27" t="inlineStr">
+        <is>
+          <t>Carne molida, cebada, leche, tomate</t>
+        </is>
+      </c>
+      <c r="K219" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L219" s="28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M219" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N219" s="30">
+        <f>IFERROR(L219/M219,"")</f>
+        <v/>
+      </c>
+      <c r="O219" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P219" s="31">
+        <f>IF(N219="","",IF(N219&gt;0.32,"Reprice or resource",IF(N219&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="27" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="27" t="inlineStr">
+        <is>
+          <t>Chupe de Cangrejo, Avena</t>
+        </is>
+      </c>
+      <c r="C220" s="27" t="inlineStr">
+        <is>
+          <t>Chupe</t>
+        </is>
+      </c>
+      <c r="D220" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E220" s="27" t="inlineStr">
+        <is>
+          <t>Bowl</t>
+        </is>
+      </c>
+      <c r="F220" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: oats thicken the chupe instead of rice, the way a partan bree is thickened. Crab is veda-bound, so the planner blocks it outright in closed months.</t>
+        </is>
+      </c>
+      <c r="G220" s="27" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="H220" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I220" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J220" s="27" t="inlineStr">
+        <is>
+          <t>Cangrejo, avena, leche, aji amarillo</t>
+        </is>
+      </c>
+      <c r="K220" s="27" t="inlineStr">
+        <is>
+          <t>Terminal Pesquero</t>
+        </is>
+      </c>
+      <c r="L220" s="28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M220" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="N220" s="30">
+        <f>IFERROR(L220/M220,"")</f>
+        <v/>
+      </c>
+      <c r="O220" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P220" s="31">
+        <f>IF(N220="","",IF(N220&gt;0.32,"Reprice or resource",IF(N220&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="27" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="27" t="inlineStr">
+        <is>
+          <t>Tamalito Verde, Mantequilla de Muna</t>
+        </is>
+      </c>
+      <c r="C221" s="27" t="inlineStr">
+        <is>
+          <t>Tamal</t>
+        </is>
+      </c>
+      <c r="D221" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E221" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F221" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: the green tamalito served the way a Scottish table serves a bannock - warm, with a whipped herb butter rather than salsa criolla.</t>
+        </is>
+      </c>
+      <c r="G221" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H221" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I221" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J221" s="27" t="inlineStr">
+        <is>
+          <t>Choclo, culantro, muna, mantequilla</t>
+        </is>
+      </c>
+      <c r="K221" s="27" t="inlineStr">
+        <is>
+          <t>Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L221" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M221" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N221" s="30">
+        <f>IFERROR(L221/M221,"")</f>
+        <v/>
+      </c>
+      <c r="O221" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P221" s="31">
+        <f>IF(N221="","",IF(N221&gt;0.32,"Reprice or resource",IF(N221&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="27" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="27" t="inlineStr">
+        <is>
+          <t>Anticucho de Alpaca, Enebro</t>
+        </is>
+      </c>
+      <c r="C222" s="27" t="inlineStr">
+        <is>
+          <t>Anticucho</t>
+        </is>
+      </c>
+      <c r="D222" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E222" s="27" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F222" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: alpaca in a panca marinade cut with juniper, skewered and grilled. The Highland game plate written as street food.</t>
+        </is>
+      </c>
+      <c r="G222" s="27" t="inlineStr">
+        <is>
+          <t>Live station</t>
+        </is>
+      </c>
+      <c r="H222" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I222" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J222" s="27" t="inlineStr">
+        <is>
+          <t>Alpaca, aji panca, enebro, vinagre</t>
+        </is>
+      </c>
+      <c r="K222" s="27" t="inlineStr">
+        <is>
+          <t>Mercado de Magdalena</t>
+        </is>
+      </c>
+      <c r="L222" s="28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M222" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N222" s="30">
+        <f>IFERROR(L222/M222,"")</f>
+        <v/>
+      </c>
+      <c r="O222" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P222" s="31">
+        <f>IF(N222="","",IF(N222&gt;0.32,"Reprice or resource",IF(N222&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="27" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="27" t="inlineStr">
+        <is>
+          <t>Salchicha Huachana con Avena</t>
+        </is>
+      </c>
+      <c r="C223" s="27" t="inlineStr">
+        <is>
+          <t>Salchicha huachana</t>
+        </is>
+      </c>
+      <c r="D223" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E223" s="27" t="inlineStr">
+        <is>
+          <t>Canape</t>
+        </is>
+      </c>
+      <c r="F223" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: the Huacho sausage bound with oats the way a Lorne square is, then cut in squares and griddled rather than crumbled.</t>
+        </is>
+      </c>
+      <c r="G223" s="27" t="inlineStr">
+        <is>
+          <t>Live station</t>
+        </is>
+      </c>
+      <c r="H223" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I223" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J223" s="27" t="inlineStr">
+        <is>
+          <t>Cerdo, aji amarillo, avena, achiote</t>
+        </is>
+      </c>
+      <c r="K223" s="27" t="inlineStr">
+        <is>
+          <t>Mercado de Magdalena</t>
+        </is>
+      </c>
+      <c r="L223" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M223" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N223" s="30">
+        <f>IFERROR(L223/M223,"")</f>
+        <v/>
+      </c>
+      <c r="O223" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P223" s="31">
+        <f>IF(N223="","",IF(N223&gt;0.32,"Reprice or resource",IF(N223&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="27" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="27" t="inlineStr">
+        <is>
+          <t>Bizcocho de Quinua y Lucuma</t>
+        </is>
+      </c>
+      <c r="C224" s="27" t="inlineStr">
+        <is>
+          <t>Bizcocho</t>
+        </is>
+      </c>
+      <c r="D224" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="E224" s="27" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="F224" s="27" t="inlineStr">
+        <is>
+          <t>Peruvian base, Scottish move: a quinoa-flour sponge built to the density of a Scottish tea loaf, with lucuma buttercream. It slices for a stand rather than a plate.</t>
+        </is>
+      </c>
+      <c r="G224" s="27" t="inlineStr">
+        <is>
+          <t>Drop-off</t>
+        </is>
+      </c>
+      <c r="H224" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I224" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J224" s="27" t="inlineStr">
+        <is>
+          <t>Quinua, lucuma, mantequilla, huevo</t>
+        </is>
+      </c>
+      <c r="K224" s="27" t="inlineStr">
+        <is>
+          <t>Makro; Surquillo N.1</t>
+        </is>
+      </c>
+      <c r="L224" s="28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M224" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N224" s="30">
+        <f>IFERROR(L224/M224,"")</f>
+        <v/>
+      </c>
+      <c r="O224" s="31" t="inlineStr">
+        <is>
+          <t>No - estimate</t>
+        </is>
+      </c>
+      <c r="P224" s="31">
+        <f>IF(N224="","",IF(N224&gt;0.32,"Reprice or resource",IF(N224&lt;0.2,"Check cost is realistic","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="34" t="inlineStr">
+        <is>
+          <t>Portfolio average</t>
+        </is>
+      </c>
+      <c r="L226" s="18">
+        <f>AVERAGE(L2:L224)</f>
+        <v/>
+      </c>
+      <c r="M226" s="18">
+        <f>AVERAGE(M2:M224)</f>
+        <v/>
+      </c>
+      <c r="N226" s="18">
+        <f>IFERROR(L226/M226,"")</f>
+        <v/>
+      </c>
+      <c r="P226" s="18">
+        <f>IF(N226&gt;0.32,"Portfolio food cost too high","Portfolio food cost OK")</f>
         <v/>
       </c>
     </row>
@@ -15019,7 +17411,7 @@
         </is>
       </c>
       <c r="B4" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"Scottish")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"Scottish")</f>
         <v/>
       </c>
       <c r="C4" s="32">
@@ -15041,7 +17433,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"Scottish (Glasgow)")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"Scottish (Glasgow)")</f>
         <v/>
       </c>
       <c r="C5" s="32">
@@ -15058,7 +17450,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"English")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"English")</f>
         <v/>
       </c>
       <c r="C6" s="32">
@@ -15080,7 +17472,7 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"Greek")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"Greek")</f>
         <v/>
       </c>
       <c r="C7" s="32">
@@ -15102,7 +17494,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"Nordic")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"Nordic")</f>
         <v/>
       </c>
       <c r="C8" s="32">
@@ -15124,7 +17516,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"Basque")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"Basque")</f>
         <v/>
       </c>
       <c r="C9" s="32">
@@ -15146,7 +17538,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"Peruvian")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"Peruvian")</f>
         <v/>
       </c>
       <c r="C10" s="32">
@@ -15163,7 +17555,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>COUNTIF(Matrix!$D$2:$D$192,"Disputed (Lake District / Scotland)")</f>
+        <f>COUNTIF(Matrix!$D$2:$D$224,"Disputed (Lake District / Scotland)")</f>
         <v/>
       </c>
       <c r="C11" s="32">
@@ -15223,7 +17615,7 @@
         </is>
       </c>
       <c r="B16" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$192,"Drop-off")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$224,"Drop-off")</f>
         <v/>
       </c>
       <c r="C16" s="23" t="n"/>
@@ -15237,7 +17629,7 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$192,"Buffet")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$224,"Buffet")</f>
         <v/>
       </c>
       <c r="C17" s="23" t="n"/>
@@ -15251,7 +17643,7 @@
         </is>
       </c>
       <c r="B18" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$192,"Plated")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$224,"Plated")</f>
         <v/>
       </c>
       <c r="C18" s="23" t="n"/>
@@ -15265,7 +17657,7 @@
         </is>
       </c>
       <c r="B19" s="23">
-        <f>COUNTIF(Matrix!$G$2:$G$192,"Live station")</f>
+        <f>COUNTIF(Matrix!$G$2:$G$224,"Live station")</f>
         <v/>
       </c>
       <c r="C19" s="23" t="n"/>
@@ -15286,7 +17678,7 @@
         </is>
       </c>
       <c r="B21" s="22">
-        <f>COUNTIF(Matrix!$H$2:$H$192,"No")</f>
+        <f>COUNTIF(Matrix!$H$2:$H$224,"No")</f>
         <v/>
       </c>
       <c r="C21" s="23" t="n"/>
@@ -15300,7 +17692,7 @@
         </is>
       </c>
       <c r="B22" s="22">
-        <f>COUNTIF(Matrix!$I$2:$I$192,"Yes")</f>
+        <f>COUNTIF(Matrix!$I$2:$I$224,"Yes")</f>
         <v/>
       </c>
       <c r="C22" s="23" t="n"/>
@@ -15321,7 +17713,7 @@
         </is>
       </c>
       <c r="B24" s="22">
-        <f>COUNTIF(Matrix!$O$2:$O$192,"No - estimate")</f>
+        <f>COUNTIF(Matrix!$O$2:$O$224,"No - estimate")</f>
         <v/>
       </c>
       <c r="C24" s="23" t="inlineStr">
